--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746627</v>
+        <v>122746617</v>
       </c>
       <c r="B2" t="n">
-        <v>90837</v>
+        <v>79747</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734717</v>
+        <v>734682</v>
       </c>
       <c r="R2" t="n">
-        <v>7125195</v>
+        <v>7125052</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746616</v>
+        <v>122746629</v>
       </c>
       <c r="B3" t="n">
-        <v>79645</v>
+        <v>90958</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lidmyran NÖ, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734706</v>
+        <v>734618</v>
       </c>
       <c r="R3" t="n">
-        <v>7125048</v>
+        <v>7125330</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122746620</v>
       </c>
       <c r="B4" t="n">
-        <v>79645</v>
+        <v>79747</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746617</v>
+        <v>122746616</v>
       </c>
       <c r="B5" t="n">
-        <v>79645</v>
+        <v>79747</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,14 +1029,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lidmyran Ö, Vb</t>
+          <t>Lidmyran NÖ, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>734682</v>
+        <v>734706</v>
       </c>
       <c r="R5" t="n">
-        <v>7125052</v>
+        <v>7125048</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746621</v>
+        <v>122746627</v>
       </c>
       <c r="B6" t="n">
-        <v>79645</v>
+        <v>90940</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>734667</v>
+        <v>734717</v>
       </c>
       <c r="R6" t="n">
-        <v>7125051</v>
+        <v>7125195</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746628</v>
+        <v>122746621</v>
       </c>
       <c r="B7" t="n">
-        <v>91525</v>
+        <v>79747</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>734624</v>
+        <v>734667</v>
       </c>
       <c r="R7" t="n">
-        <v>7125327</v>
+        <v>7125051</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746629</v>
+        <v>122746628</v>
       </c>
       <c r="B8" t="n">
-        <v>90855</v>
+        <v>91628</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>734618</v>
+        <v>734624</v>
       </c>
       <c r="R8" t="n">
-        <v>7125330</v>
+        <v>7125327</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746617</v>
+        <v>122746629</v>
       </c>
       <c r="B2" t="n">
-        <v>79747</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lidmyran Ö, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734682</v>
+        <v>734618</v>
       </c>
       <c r="R2" t="n">
-        <v>7125052</v>
+        <v>7125330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746629</v>
+        <v>122746616</v>
       </c>
       <c r="B3" t="n">
-        <v>90958</v>
+        <v>79751</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran NÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734618</v>
+        <v>734706</v>
       </c>
       <c r="R3" t="n">
-        <v>7125330</v>
+        <v>7125048</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122746620</v>
       </c>
       <c r="B4" t="n">
-        <v>79747</v>
+        <v>79751</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746616</v>
+        <v>122746621</v>
       </c>
       <c r="B5" t="n">
-        <v>79747</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,14 +1029,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lidmyran NÖ, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>734706</v>
+        <v>734667</v>
       </c>
       <c r="R5" t="n">
-        <v>7125048</v>
+        <v>7125051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1102,7 @@
         <v>122746627</v>
       </c>
       <c r="B6" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746621</v>
+        <v>122746628</v>
       </c>
       <c r="B7" t="n">
-        <v>79747</v>
+        <v>91632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>734667</v>
+        <v>734624</v>
       </c>
       <c r="R7" t="n">
-        <v>7125051</v>
+        <v>7125327</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746628</v>
+        <v>122746617</v>
       </c>
       <c r="B8" t="n">
-        <v>91628</v>
+        <v>79751</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>734624</v>
+        <v>734682</v>
       </c>
       <c r="R8" t="n">
-        <v>7125327</v>
+        <v>7125052</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746629</v>
+        <v>122746627</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734618</v>
+        <v>734717</v>
       </c>
       <c r="R2" t="n">
-        <v>7125330</v>
+        <v>7125195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746616</v>
+        <v>122746620</v>
       </c>
       <c r="B3" t="n">
         <v>79751</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lidmyran NÖ, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734706</v>
+        <v>734544</v>
       </c>
       <c r="R3" t="n">
-        <v>7125048</v>
+        <v>7125057</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746620</v>
+        <v>122746621</v>
       </c>
       <c r="B4" t="n">
         <v>79751</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734544</v>
+        <v>734667</v>
       </c>
       <c r="R4" t="n">
-        <v>7125057</v>
+        <v>7125051</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746621</v>
+        <v>122746628</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>91632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>734667</v>
+        <v>734624</v>
       </c>
       <c r="R5" t="n">
-        <v>7125051</v>
+        <v>7125327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746627</v>
+        <v>122746629</v>
       </c>
       <c r="B6" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>734717</v>
+        <v>734618</v>
       </c>
       <c r="R6" t="n">
-        <v>7125195</v>
+        <v>7125330</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746628</v>
+        <v>122746617</v>
       </c>
       <c r="B7" t="n">
-        <v>91632</v>
+        <v>79751</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>734624</v>
+        <v>734682</v>
       </c>
       <c r="R7" t="n">
-        <v>7125327</v>
+        <v>7125052</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746617</v>
+        <v>122746616</v>
       </c>
       <c r="B8" t="n">
         <v>79751</v>
@@ -1347,14 +1347,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lidmyran Ö, Vb</t>
+          <t>Lidmyran NÖ, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>734682</v>
+        <v>734706</v>
       </c>
       <c r="R8" t="n">
-        <v>7125052</v>
+        <v>7125048</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746627</v>
+        <v>122746616</v>
       </c>
       <c r="B2" t="n">
-        <v>90944</v>
+        <v>79751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran NÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734717</v>
+        <v>734706</v>
       </c>
       <c r="R2" t="n">
-        <v>7125195</v>
+        <v>7125048</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746621</v>
+        <v>122746627</v>
       </c>
       <c r="B4" t="n">
-        <v>79751</v>
+        <v>90944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734667</v>
+        <v>734717</v>
       </c>
       <c r="R4" t="n">
-        <v>7125051</v>
+        <v>7125195</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746628</v>
+        <v>122746617</v>
       </c>
       <c r="B5" t="n">
-        <v>91632</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>734624</v>
+        <v>734682</v>
       </c>
       <c r="R5" t="n">
-        <v>7125327</v>
+        <v>7125052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746629</v>
+        <v>122746628</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>91632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>734618</v>
+        <v>734624</v>
       </c>
       <c r="R6" t="n">
-        <v>7125330</v>
+        <v>7125327</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746617</v>
+        <v>122746621</v>
       </c>
       <c r="B7" t="n">
         <v>79751</v>
@@ -1241,14 +1241,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lidmyran Ö, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>734682</v>
+        <v>734667</v>
       </c>
       <c r="R7" t="n">
-        <v>7125052</v>
+        <v>7125051</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746616</v>
+        <v>122746629</v>
       </c>
       <c r="B8" t="n">
-        <v>79751</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lidmyran NÖ, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>734706</v>
+        <v>734618</v>
       </c>
       <c r="R8" t="n">
-        <v>7125048</v>
+        <v>7125330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746616</v>
+        <v>122746628</v>
       </c>
       <c r="B2" t="n">
-        <v>79751</v>
+        <v>91632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lidmyran NÖ, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734706</v>
+        <v>734624</v>
       </c>
       <c r="R2" t="n">
-        <v>7125048</v>
+        <v>7125327</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746620</v>
+        <v>122746627</v>
       </c>
       <c r="B3" t="n">
-        <v>79751</v>
+        <v>90944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734544</v>
+        <v>734717</v>
       </c>
       <c r="R3" t="n">
-        <v>7125057</v>
+        <v>7125195</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746627</v>
+        <v>122746629</v>
       </c>
       <c r="B4" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734717</v>
+        <v>734618</v>
       </c>
       <c r="R4" t="n">
-        <v>7125195</v>
+        <v>7125330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746617</v>
+        <v>122746621</v>
       </c>
       <c r="B5" t="n">
         <v>79751</v>
@@ -1029,14 +1029,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lidmyran Ö, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>734682</v>
+        <v>734667</v>
       </c>
       <c r="R5" t="n">
-        <v>7125052</v>
+        <v>7125051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746628</v>
+        <v>122746617</v>
       </c>
       <c r="B6" t="n">
-        <v>91632</v>
+        <v>79751</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>734624</v>
+        <v>734682</v>
       </c>
       <c r="R6" t="n">
-        <v>7125327</v>
+        <v>7125052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746621</v>
+        <v>122746616</v>
       </c>
       <c r="B7" t="n">
         <v>79751</v>
@@ -1241,14 +1241,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Lidmyran NÖ, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>734667</v>
+        <v>734706</v>
       </c>
       <c r="R7" t="n">
-        <v>7125051</v>
+        <v>7125048</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746629</v>
+        <v>122746620</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>79751</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>734618</v>
+        <v>734544</v>
       </c>
       <c r="R8" t="n">
-        <v>7125330</v>
+        <v>7125057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746628</v>
+        <v>122746629</v>
       </c>
       <c r="B2" t="n">
-        <v>91632</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734624</v>
+        <v>734618</v>
       </c>
       <c r="R2" t="n">
-        <v>7125327</v>
+        <v>7125330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746627</v>
+        <v>122746617</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
+        <v>79751</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734717</v>
+        <v>734682</v>
       </c>
       <c r="R3" t="n">
-        <v>7125195</v>
+        <v>7125052</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746629</v>
+        <v>122746628</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>91640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734618</v>
+        <v>734624</v>
       </c>
       <c r="R4" t="n">
-        <v>7125330</v>
+        <v>7125327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746617</v>
+        <v>122746616</v>
       </c>
       <c r="B6" t="n">
         <v>79751</v>
@@ -1135,14 +1135,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lidmyran Ö, Vb</t>
+          <t>Lidmyran NÖ, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>734682</v>
+        <v>734706</v>
       </c>
       <c r="R6" t="n">
-        <v>7125052</v>
+        <v>7125048</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746616</v>
+        <v>122746620</v>
       </c>
       <c r="B7" t="n">
         <v>79751</v>
@@ -1241,14 +1241,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lidmyran NÖ, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>734706</v>
+        <v>734544</v>
       </c>
       <c r="R7" t="n">
-        <v>7125048</v>
+        <v>7125057</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746620</v>
+        <v>122746627</v>
       </c>
       <c r="B8" t="n">
-        <v>79751</v>
+        <v>90952</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>734544</v>
+        <v>734717</v>
       </c>
       <c r="R8" t="n">
-        <v>7125057</v>
+        <v>7125195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746629</v>
+        <v>122746627</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734618</v>
+        <v>734717</v>
       </c>
       <c r="R2" t="n">
-        <v>7125330</v>
+        <v>7125195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746617</v>
+        <v>122746628</v>
       </c>
       <c r="B3" t="n">
-        <v>79751</v>
+        <v>91640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lidmyran Ö, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734682</v>
+        <v>734624</v>
       </c>
       <c r="R3" t="n">
-        <v>7125052</v>
+        <v>7125327</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746628</v>
+        <v>122746617</v>
       </c>
       <c r="B4" t="n">
-        <v>91640</v>
+        <v>79751</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734624</v>
+        <v>734682</v>
       </c>
       <c r="R4" t="n">
-        <v>7125327</v>
+        <v>7125052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746621</v>
+        <v>122746616</v>
       </c>
       <c r="B5" t="n">
         <v>79751</v>
@@ -1029,14 +1029,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Lidmyran NÖ, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>734667</v>
+        <v>734706</v>
       </c>
       <c r="R5" t="n">
-        <v>7125051</v>
+        <v>7125048</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746616</v>
+        <v>122746621</v>
       </c>
       <c r="B6" t="n">
         <v>79751</v>
@@ -1135,14 +1135,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lidmyran NÖ, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>734706</v>
+        <v>734667</v>
       </c>
       <c r="R6" t="n">
-        <v>7125048</v>
+        <v>7125051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746627</v>
+        <v>122746629</v>
       </c>
       <c r="B8" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>734717</v>
+        <v>734618</v>
       </c>
       <c r="R8" t="n">
-        <v>7125195</v>
+        <v>7125330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746627</v>
+        <v>122746629</v>
       </c>
       <c r="B2" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734717</v>
+        <v>734618</v>
       </c>
       <c r="R2" t="n">
-        <v>7125195</v>
+        <v>7125330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746628</v>
+        <v>122746620</v>
       </c>
       <c r="B3" t="n">
-        <v>91640</v>
+        <v>79751</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734624</v>
+        <v>734544</v>
       </c>
       <c r="R3" t="n">
-        <v>7125327</v>
+        <v>7125057</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746617</v>
+        <v>122746628</v>
       </c>
       <c r="B4" t="n">
-        <v>79751</v>
+        <v>91640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lidmyran Ö, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734682</v>
+        <v>734624</v>
       </c>
       <c r="R4" t="n">
-        <v>7125052</v>
+        <v>7125327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746620</v>
+        <v>122746617</v>
       </c>
       <c r="B7" t="n">
         <v>79751</v>
@@ -1241,14 +1241,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Lidmyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>734544</v>
+        <v>734682</v>
       </c>
       <c r="R7" t="n">
-        <v>7125057</v>
+        <v>7125052</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746629</v>
+        <v>122746627</v>
       </c>
       <c r="B8" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>734618</v>
+        <v>734717</v>
       </c>
       <c r="R8" t="n">
-        <v>7125330</v>
+        <v>7125195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746629</v>
+        <v>122746617</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>79751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734618</v>
+        <v>734682</v>
       </c>
       <c r="R2" t="n">
-        <v>7125330</v>
+        <v>7125052</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746620</v>
+        <v>122746616</v>
       </c>
       <c r="B3" t="n">
         <v>79751</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Lidmyran NÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734544</v>
+        <v>734706</v>
       </c>
       <c r="R3" t="n">
-        <v>7125057</v>
+        <v>7125048</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746628</v>
+        <v>122746621</v>
       </c>
       <c r="B4" t="n">
-        <v>91640</v>
+        <v>79751</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734624</v>
+        <v>734667</v>
       </c>
       <c r="R4" t="n">
-        <v>7125327</v>
+        <v>7125051</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746616</v>
+        <v>122746620</v>
       </c>
       <c r="B5" t="n">
         <v>79751</v>
@@ -1029,14 +1029,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lidmyran NÖ, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>734706</v>
+        <v>734544</v>
       </c>
       <c r="R5" t="n">
-        <v>7125048</v>
+        <v>7125057</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746621</v>
+        <v>122746629</v>
       </c>
       <c r="B6" t="n">
-        <v>79751</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>734667</v>
+        <v>734618</v>
       </c>
       <c r="R6" t="n">
-        <v>7125051</v>
+        <v>7125330</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746617</v>
+        <v>122746628</v>
       </c>
       <c r="B7" t="n">
-        <v>79751</v>
+        <v>91640</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lidmyran Ö, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>734682</v>
+        <v>734624</v>
       </c>
       <c r="R7" t="n">
-        <v>7125052</v>
+        <v>7125327</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746617</v>
+        <v>122746627</v>
       </c>
       <c r="B2" t="n">
-        <v>79751</v>
+        <v>90955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lidmyran Ö, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734682</v>
+        <v>734717</v>
       </c>
       <c r="R2" t="n">
-        <v>7125052</v>
+        <v>7125195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122746616</v>
       </c>
       <c r="B3" t="n">
-        <v>79751</v>
+        <v>79754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746621</v>
+        <v>122746629</v>
       </c>
       <c r="B4" t="n">
-        <v>79751</v>
+        <v>90973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734667</v>
+        <v>734618</v>
       </c>
       <c r="R4" t="n">
-        <v>7125051</v>
+        <v>7125330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746620</v>
+        <v>122746628</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>91643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>734544</v>
+        <v>734624</v>
       </c>
       <c r="R5" t="n">
-        <v>7125057</v>
+        <v>7125327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746629</v>
+        <v>122746621</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>79754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>734618</v>
+        <v>734667</v>
       </c>
       <c r="R6" t="n">
-        <v>7125330</v>
+        <v>7125051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746628</v>
+        <v>122746620</v>
       </c>
       <c r="B7" t="n">
-        <v>91640</v>
+        <v>79754</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>734624</v>
+        <v>734544</v>
       </c>
       <c r="R7" t="n">
-        <v>7125327</v>
+        <v>7125057</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746627</v>
+        <v>122746617</v>
       </c>
       <c r="B8" t="n">
-        <v>90952</v>
+        <v>79754</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>734717</v>
+        <v>734682</v>
       </c>
       <c r="R8" t="n">
-        <v>7125195</v>
+        <v>7125052</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746627</v>
+        <v>122746621</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>79756</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734717</v>
+        <v>734667</v>
       </c>
       <c r="R2" t="n">
-        <v>7125195</v>
+        <v>7125051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746616</v>
+        <v>122746620</v>
       </c>
       <c r="B3" t="n">
-        <v>79754</v>
+        <v>79756</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lidmyran NÖ, Vb</t>
+          <t>Rörvik SV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734706</v>
+        <v>734544</v>
       </c>
       <c r="R3" t="n">
-        <v>7125048</v>
+        <v>7125057</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746629</v>
+        <v>122746617</v>
       </c>
       <c r="B4" t="n">
-        <v>90973</v>
+        <v>79756</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734618</v>
+        <v>734682</v>
       </c>
       <c r="R4" t="n">
-        <v>7125330</v>
+        <v>7125052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746628</v>
+        <v>122746616</v>
       </c>
       <c r="B5" t="n">
-        <v>91643</v>
+        <v>79756</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sanatorieberget SV, Vb</t>
+          <t>Lidmyran NÖ, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>734624</v>
+        <v>734706</v>
       </c>
       <c r="R5" t="n">
-        <v>7125327</v>
+        <v>7125048</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746621</v>
+        <v>122746627</v>
       </c>
       <c r="B6" t="n">
-        <v>79754</v>
+        <v>90957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>734667</v>
+        <v>734717</v>
       </c>
       <c r="R6" t="n">
-        <v>7125051</v>
+        <v>7125195</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746620</v>
+        <v>122746628</v>
       </c>
       <c r="B7" t="n">
-        <v>79754</v>
+        <v>91645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörvik SV, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>734544</v>
+        <v>734624</v>
       </c>
       <c r="R7" t="n">
-        <v>7125057</v>
+        <v>7125327</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746617</v>
+        <v>122746629</v>
       </c>
       <c r="B8" t="n">
-        <v>79754</v>
+        <v>90975</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lidmyran Ö, Vb</t>
+          <t>Sanatorieberget SV, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>734682</v>
+        <v>734618</v>
       </c>
       <c r="R8" t="n">
-        <v>7125052</v>
+        <v>7125330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122746621</v>
       </c>
       <c r="B2" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122746620</v>
       </c>
       <c r="B3" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122746617</v>
       </c>
       <c r="B4" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122746616</v>
       </c>
       <c r="B5" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122746627</v>
       </c>
       <c r="B6" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122746628</v>
       </c>
       <c r="B7" t="n">
-        <v>92612</v>
+        <v>92615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122746629</v>
       </c>
       <c r="B8" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122746621</v>
       </c>
       <c r="B2" t="n">
-        <v>80326</v>
+        <v>80328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122746620</v>
       </c>
       <c r="B3" t="n">
-        <v>80326</v>
+        <v>80328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122746617</v>
       </c>
       <c r="B4" t="n">
-        <v>80326</v>
+        <v>80328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122746616</v>
       </c>
       <c r="B5" t="n">
-        <v>80326</v>
+        <v>80328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122746627</v>
       </c>
       <c r="B6" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122746628</v>
       </c>
       <c r="B7" t="n">
-        <v>92615</v>
+        <v>92621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122746629</v>
       </c>
       <c r="B8" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122746621</v>
       </c>
       <c r="B2" t="n">
-        <v>80328</v>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122746620</v>
       </c>
       <c r="B3" t="n">
-        <v>80328</v>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122746617</v>
       </c>
       <c r="B4" t="n">
-        <v>80328</v>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122746616</v>
       </c>
       <c r="B5" t="n">
-        <v>80328</v>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122746627</v>
       </c>
       <c r="B6" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122746628</v>
       </c>
       <c r="B7" t="n">
-        <v>92621</v>
+        <v>92631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122746629</v>
       </c>
       <c r="B8" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -1082,7 +1082,7 @@
         <v>122746627</v>
       </c>
       <c r="B6" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122746628</v>
       </c>
       <c r="B7" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122746629</v>
       </c>
       <c r="B8" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122746621</v>
       </c>
       <c r="B2" t="n">
-        <v>80336</v>
+        <v>80337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122746620</v>
       </c>
       <c r="B3" t="n">
-        <v>80336</v>
+        <v>80337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122746617</v>
       </c>
       <c r="B4" t="n">
-        <v>80336</v>
+        <v>80337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122746616</v>
       </c>
       <c r="B5" t="n">
-        <v>80336</v>
+        <v>80337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122746627</v>
       </c>
       <c r="B6" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122746628</v>
       </c>
       <c r="B7" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122746629</v>
       </c>
       <c r="B8" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -1082,7 +1082,7 @@
         <v>122746627</v>
       </c>
       <c r="B6" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122746628</v>
       </c>
       <c r="B7" t="n">
-        <v>92633</v>
+        <v>92635</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122746629</v>
       </c>
       <c r="B8" t="n">
-        <v>91930</v>
+        <v>91932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40760-2024 artfynd.xlsx
+++ b/artfynd/A 40760-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122746621</v>
       </c>
       <c r="B2" t="n">
-        <v>80337</v>
+        <v>80338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122746620</v>
       </c>
       <c r="B3" t="n">
-        <v>80337</v>
+        <v>80338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122746617</v>
       </c>
       <c r="B4" t="n">
-        <v>80337</v>
+        <v>80338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122746616</v>
       </c>
       <c r="B5" t="n">
-        <v>80337</v>
+        <v>80338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122746627</v>
       </c>
       <c r="B6" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122746628</v>
       </c>
       <c r="B7" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122746629</v>
       </c>
       <c r="B8" t="n">
-        <v>91932</v>
+        <v>91933</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
